--- a/administrative_forms/003_onsite_dynamic_risk_assessment_form--administrative_forms.xlsx
+++ b/administrative_forms/003_onsite_dynamic_risk_assessment_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -607,7 +607,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>hh:mm AM/PM</t>
+          <t>hh -mm AM/PM</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>risk_description</t>
+          <t>risk_description_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Risk Description</t>
+          <t>Risk Description 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>risk_frequency</t>
+          <t>risk_frequency_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How often do you see this type of risk</t>
+          <t>Risk Frequency 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -890,12 +890,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>risk_level_impact</t>
+          <t>risk_level_impact_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What is the risk level impact</t>
+          <t>Risk Level Impact 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>risk_urgency</t>
+          <t>risk_urgency_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What is the risk urgency</t>
+          <t>Risk Urgency 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -936,12 +936,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>risk_priority</t>
+          <t>risk_priority_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What is the risk priority</t>
+          <t>Risk Priority 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -996,7 +996,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>hh:mm AM/PM</t>
+          <t>hh -mm AM/PM</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>hh:mm AM/PM</t>
+          <t>hh -mm AM/PM</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
